--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NicolasDuranPoveda\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unigermana-my.sharepoint.com/personal/tecnico_tecnologia_unigermana_edu_co/Documents/Escritorio/Api-python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5D6E3C3-4A62-486D-B55A-DCB486ECFC80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{F5D6E3C3-4A62-486D-B55A-DCB486ECFC80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B916B3B0-F982-4B5F-980D-5DEABA73E877}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{B33F2633-1FE2-4BB3-97DC-D74CD3B8832A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B33F2633-1FE2-4BB3-97DC-D74CD3B8832A}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$G$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -66,7 +69,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,7 +109,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -444,9 +447,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{456ABCB0-78C7-4556-BDA1-A91B17080E3B}">
   <dimension ref="A1:G248"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -469,7 +472,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>50000</v>
       </c>
@@ -492,7 +495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>35000</v>
       </c>
@@ -515,7 +518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>70000</v>
       </c>
@@ -538,7 +541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>44000</v>
       </c>
@@ -561,7 +564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>60000</v>
       </c>
@@ -584,7 +587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>30000</v>
       </c>
@@ -607,7 +610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>80000</v>
       </c>
@@ -630,7 +633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>20000</v>
       </c>
@@ -653,7 +656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>45000</v>
       </c>
@@ -676,7 +679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>38000</v>
       </c>
@@ -699,7 +702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>90000</v>
       </c>
@@ -722,7 +725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>100000</v>
       </c>
@@ -745,7 +748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>110000</v>
       </c>
@@ -768,7 +771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>85000</v>
       </c>
@@ -791,7 +794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>95000</v>
       </c>
@@ -814,7 +817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>70000</v>
       </c>
@@ -837,7 +840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>120000</v>
       </c>
@@ -860,7 +863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>105000</v>
       </c>
@@ -883,7 +886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>99000</v>
       </c>
@@ -906,7 +909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>87000</v>
       </c>
@@ -929,7 +932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>48000</v>
       </c>
@@ -952,7 +955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>36000</v>
       </c>
@@ -975,7 +978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>72000</v>
       </c>
@@ -998,7 +1001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>46000</v>
       </c>
@@ -1021,7 +1024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>61000</v>
       </c>
@@ -1044,7 +1047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>31000</v>
       </c>
@@ -1067,7 +1070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>82000</v>
       </c>
@@ -1090,7 +1093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>21000</v>
       </c>
@@ -1113,7 +1116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>47000</v>
       </c>
@@ -1136,7 +1139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>39000</v>
       </c>
@@ -1159,7 +1162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>91000</v>
       </c>
@@ -1182,7 +1185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>101000</v>
       </c>
@@ -1205,7 +1208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>111000</v>
       </c>
@@ -1228,7 +1231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>86000</v>
       </c>
@@ -1251,7 +1254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>96000</v>
       </c>
@@ -1274,7 +1277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>71000</v>
       </c>
@@ -1297,7 +1300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>121000</v>
       </c>
@@ -1320,7 +1323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>106000</v>
       </c>
@@ -1343,7 +1346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>100000</v>
       </c>
@@ -1366,7 +1369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>88000</v>
       </c>
@@ -1389,7 +1392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>49000</v>
       </c>
@@ -1412,7 +1415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>37000</v>
       </c>
@@ -1435,7 +1438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>73000</v>
       </c>
@@ -1458,7 +1461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>47000</v>
       </c>
@@ -1481,7 +1484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>62000</v>
       </c>
@@ -1504,7 +1507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>32000</v>
       </c>
@@ -1527,7 +1530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>83000</v>
       </c>
@@ -1550,7 +1553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>22000</v>
       </c>
@@ -1573,7 +1576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>48000</v>
       </c>
@@ -1596,7 +1599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>40000</v>
       </c>
@@ -1619,7 +1622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>85000</v>
       </c>
@@ -1642,7 +1645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>42000</v>
       </c>
@@ -1665,7 +1668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>98000</v>
       </c>
@@ -1688,7 +1691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>30000</v>
       </c>
@@ -1711,7 +1714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>76000</v>
       </c>
@@ -1734,7 +1737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>22000</v>
       </c>
@@ -1757,7 +1760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>110000</v>
       </c>
@@ -1780,7 +1783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>65000</v>
       </c>
@@ -1803,7 +1806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>43000</v>
       </c>
@@ -1826,7 +1829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>99000</v>
       </c>
@@ -1849,7 +1852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>78000</v>
       </c>
@@ -1872,7 +1875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>36000</v>
       </c>
@@ -1895,7 +1898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>92000</v>
       </c>
@@ -1918,7 +1921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>48000</v>
       </c>
@@ -1941,7 +1944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>70000</v>
       </c>
@@ -1964,7 +1967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>25000</v>
       </c>
@@ -1987,7 +1990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>87000</v>
       </c>
@@ -2010,7 +2013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>54000</v>
       </c>
@@ -2033,7 +2036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>62000</v>
       </c>
@@ -2056,7 +2059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>33000</v>
       </c>
@@ -2079,7 +2082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>91000</v>
       </c>
@@ -2102,7 +2105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>47000</v>
       </c>
@@ -2125,7 +2128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>82000</v>
       </c>
@@ -2148,7 +2151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>39000</v>
       </c>
@@ -2171,7 +2174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>76000</v>
       </c>
@@ -2194,7 +2197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>28000</v>
       </c>
@@ -2217,7 +2220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>95000</v>
       </c>
@@ -2240,7 +2243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>51000</v>
       </c>
@@ -2263,7 +2266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>68000</v>
       </c>
@@ -2286,7 +2289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>34000</v>
       </c>
@@ -2309,7 +2312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>89000</v>
       </c>
@@ -2332,7 +2335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>46000</v>
       </c>
@@ -2355,7 +2358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>80000</v>
       </c>
@@ -2378,7 +2381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>37000</v>
       </c>
@@ -2401,7 +2404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>72000</v>
       </c>
@@ -2424,7 +2427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>26000</v>
       </c>
@@ -2447,7 +2450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:7">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>93000</v>
       </c>
@@ -2470,7 +2473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>50000</v>
       </c>
@@ -2493,7 +2496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:7">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>67000</v>
       </c>
@@ -2516,7 +2519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>35000</v>
       </c>
@@ -2539,7 +2542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>88000</v>
       </c>
@@ -2562,7 +2565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>45000</v>
       </c>
@@ -2585,7 +2588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>79000</v>
       </c>
@@ -2608,7 +2611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>38000</v>
       </c>
@@ -2631,7 +2634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:7">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>71000</v>
       </c>
@@ -2654,7 +2657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>24000</v>
       </c>
@@ -2677,7 +2680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>96000</v>
       </c>
@@ -2700,7 +2703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:7">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>52000</v>
       </c>
@@ -2723,7 +2726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:7">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>66000</v>
       </c>
@@ -2746,7 +2749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>32000</v>
       </c>
@@ -2769,7 +2772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>90000</v>
       </c>
@@ -2792,7 +2795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>48000</v>
       </c>
@@ -2815,7 +2818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:7">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>83000</v>
       </c>
@@ -2838,7 +2841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>36000</v>
       </c>
@@ -2861,7 +2864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>74000</v>
       </c>
@@ -2884,7 +2887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:7">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>27000</v>
       </c>
@@ -2907,7 +2910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:7">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>94000</v>
       </c>
@@ -2930,7 +2933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>53000</v>
       </c>
@@ -2953,7 +2956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>69000</v>
       </c>
@@ -2976,7 +2979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>33000</v>
       </c>
@@ -2999,7 +3002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>87000</v>
       </c>
@@ -3022,7 +3025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:7">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>47000</v>
       </c>
@@ -3045,7 +3048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:7">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>81000</v>
       </c>
@@ -3068,7 +3071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:7">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>39000</v>
       </c>
@@ -3091,7 +3094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>73000</v>
       </c>
@@ -3114,7 +3117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:7">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>25000</v>
       </c>
@@ -3137,7 +3140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:7">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>97000</v>
       </c>
@@ -3160,7 +3163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:7">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>54000</v>
       </c>
@@ -3183,7 +3186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:7">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>67000</v>
       </c>
@@ -3206,7 +3209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:7">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>34000</v>
       </c>
@@ -3229,7 +3232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>91000</v>
       </c>
@@ -3252,7 +3255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:7">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>46000</v>
       </c>
@@ -3275,7 +3278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:7">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>78000</v>
       </c>
@@ -3298,7 +3301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>37000</v>
       </c>
@@ -3321,7 +3324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>72000</v>
       </c>
@@ -3344,7 +3347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:7">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>26000</v>
       </c>
@@ -3367,7 +3370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:7">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>95000</v>
       </c>
@@ -3390,7 +3393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:7">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>52000</v>
       </c>
@@ -3413,7 +3416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:7">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>66000</v>
       </c>
@@ -3436,7 +3439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:7">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>32000</v>
       </c>
@@ -3459,7 +3462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>88000</v>
       </c>
@@ -3482,7 +3485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:7">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>45000</v>
       </c>
@@ -3505,7 +3508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:7">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>80000</v>
       </c>
@@ -3528,7 +3531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:7">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>38000</v>
       </c>
@@ -3551,7 +3554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:7">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>71000</v>
       </c>
@@ -3574,7 +3577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:7">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>24000</v>
       </c>
@@ -3597,7 +3600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:7">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>96000</v>
       </c>
@@ -3620,7 +3623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:7">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>51000</v>
       </c>
@@ -3643,7 +3646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:7">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>68000</v>
       </c>
@@ -3666,7 +3669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:7">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>35000</v>
       </c>
@@ -3689,7 +3692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:7">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>89000</v>
       </c>
@@ -3712,7 +3715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:7">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>81234</v>
       </c>
@@ -3735,7 +3738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:7">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>34567</v>
       </c>
@@ -3758,7 +3761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:7">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>92345</v>
       </c>
@@ -3781,7 +3784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:7">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>45678</v>
       </c>
@@ -3804,7 +3807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:7">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>67890</v>
       </c>
@@ -3827,7 +3830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:7">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>23456</v>
       </c>
@@ -3850,7 +3853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:7">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>105432</v>
       </c>
@@ -3873,7 +3876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:7">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>56789</v>
       </c>
@@ -3896,7 +3899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:7">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>39876</v>
       </c>
@@ -3919,7 +3922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:7">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>98765</v>
       </c>
@@ -3942,7 +3945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:7">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>75432</v>
       </c>
@@ -3965,7 +3968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:7">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>31245</v>
       </c>
@@ -3988,7 +3991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:7">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>88990</v>
       </c>
@@ -4011,7 +4014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:7">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>47890</v>
       </c>
@@ -4034,7 +4037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:7">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>66500</v>
       </c>
@@ -4057,7 +4060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:7">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>25900</v>
       </c>
@@ -4080,7 +4083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:7">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>84500</v>
       </c>
@@ -4103,7 +4106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:7">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>51200</v>
       </c>
@@ -4126,7 +4129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:7">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>60100</v>
       </c>
@@ -4149,7 +4152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:7">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>33800</v>
       </c>
@@ -4172,7 +4175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:7">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>93200</v>
       </c>
@@ -4195,7 +4198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:7">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>46700</v>
       </c>
@@ -4218,7 +4221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:7">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>82000</v>
       </c>
@@ -4241,7 +4244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:7">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>39500</v>
       </c>
@@ -4264,7 +4267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:7">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>74500</v>
       </c>
@@ -4287,7 +4290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:7">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>27500</v>
       </c>
@@ -4310,7 +4313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:7">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>96500</v>
       </c>
@@ -4333,7 +4336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:7">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>53000</v>
       </c>
@@ -4356,7 +4359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:7">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>69000</v>
       </c>
@@ -4379,7 +4382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:7">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>34000</v>
       </c>
@@ -4402,7 +4405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:7">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>90500</v>
       </c>
@@ -4425,7 +4428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:7">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>46000</v>
       </c>
@@ -4448,7 +4451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:7">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>78000</v>
       </c>
@@ -4471,7 +4474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:7">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>38000</v>
       </c>
@@ -4494,7 +4497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:7">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>72000</v>
       </c>
@@ -4517,7 +4520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:7">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>26000</v>
       </c>
@@ -4540,7 +4543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:7">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>97000</v>
       </c>
@@ -4563,7 +4566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:7">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>54000</v>
       </c>
@@ -4586,7 +4589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:7">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>67000</v>
       </c>
@@ -4609,7 +4612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:7">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>35000</v>
       </c>
@@ -4632,7 +4635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:7">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>89000</v>
       </c>
@@ -4655,7 +4658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:7">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>45000</v>
       </c>
@@ -4678,7 +4681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:7">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>80000</v>
       </c>
@@ -4701,7 +4704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:7">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>37000</v>
       </c>
@@ -4724,7 +4727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:7">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>71000</v>
       </c>
@@ -4747,7 +4750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:7">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>24000</v>
       </c>
@@ -4770,7 +4773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:7">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>96000</v>
       </c>
@@ -4793,7 +4796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:7">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>52000</v>
       </c>
@@ -4816,7 +4819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:7">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>66000</v>
       </c>
@@ -4839,7 +4842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:7">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>32000</v>
       </c>
@@ -4862,7 +4865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:7">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>88000</v>
       </c>
@@ -4885,7 +4888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:7">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>44000</v>
       </c>
@@ -4908,7 +4911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:7">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>79500</v>
       </c>
@@ -4931,7 +4934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:7">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>36500</v>
       </c>
@@ -4954,7 +4957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:7">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>70500</v>
       </c>
@@ -4977,7 +4980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:7">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>25000</v>
       </c>
@@ -5000,7 +5003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:7">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>95500</v>
       </c>
@@ -5023,7 +5026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:7">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>53500</v>
       </c>
@@ -5046,7 +5049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:7">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>67500</v>
       </c>
@@ -5069,7 +5072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:7">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>34500</v>
       </c>
@@ -5092,7 +5095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:7">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>91000</v>
       </c>
@@ -5115,7 +5118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:7">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>47000</v>
       </c>
@@ -5138,7 +5141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:7">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>78500</v>
       </c>
@@ -5161,7 +5164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:7">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>37500</v>
       </c>
@@ -5184,7 +5187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:7">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>71500</v>
       </c>
@@ -5207,7 +5210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:7">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>25500</v>
       </c>
@@ -5230,7 +5233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:7">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>96500</v>
       </c>
@@ -5253,7 +5256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:7">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>54500</v>
       </c>
@@ -5276,7 +5279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:7">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>68500</v>
       </c>
@@ -5299,7 +5302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:7">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>35500</v>
       </c>
@@ -5322,7 +5325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:7">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>89500</v>
       </c>
@@ -5345,7 +5348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:7">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>45500</v>
       </c>
@@ -5368,7 +5371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:7">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>80500</v>
       </c>
@@ -5391,7 +5394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:7">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>38500</v>
       </c>
@@ -5414,7 +5417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:7">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>72500</v>
       </c>
@@ -5437,7 +5440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:7">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>26500</v>
       </c>
@@ -5460,7 +5463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:7">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>97500</v>
       </c>
@@ -5483,7 +5486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:7">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>55000</v>
       </c>
@@ -5506,7 +5509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:7">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>69000</v>
       </c>
@@ -5529,7 +5532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:7">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>36000</v>
       </c>
@@ -5552,7 +5555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:7">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>90000</v>
       </c>
@@ -5575,7 +5578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:7">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>48000</v>
       </c>
@@ -5598,7 +5601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:7">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>82000</v>
       </c>
@@ -5621,7 +5624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:7">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>39000</v>
       </c>
@@ -5644,7 +5647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:7">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>74000</v>
       </c>
@@ -5667,7 +5670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:7">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>27000</v>
       </c>
@@ -5690,7 +5693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:7">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>98000</v>
       </c>
@@ -5713,7 +5716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:7">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>56000</v>
       </c>
@@ -5736,7 +5739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:7">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>70000</v>
       </c>
@@ -5759,7 +5762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:7">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>37000</v>
       </c>
@@ -5782,7 +5785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:7">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>91000</v>
       </c>
@@ -5805,7 +5808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:7">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>49000</v>
       </c>
@@ -5828,7 +5831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:7">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>83000</v>
       </c>
@@ -5851,7 +5854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:7">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>40000</v>
       </c>
@@ -5874,7 +5877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:7">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>75000</v>
       </c>
@@ -5897,7 +5900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:7">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>28000</v>
       </c>
@@ -5920,7 +5923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:7">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>99000</v>
       </c>
@@ -5943,7 +5946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:7">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>57000</v>
       </c>
@@ -5966,7 +5969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:7">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>71000</v>
       </c>
@@ -5989,7 +5992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:7">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>38000</v>
       </c>
@@ -6012,7 +6015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:7">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>92000</v>
       </c>
@@ -6035,7 +6038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:7">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>50000</v>
       </c>
@@ -6058,7 +6061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:7">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>84000</v>
       </c>
@@ -6081,7 +6084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:7">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>41000</v>
       </c>
@@ -6104,7 +6107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:7">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>76000</v>
       </c>
@@ -6127,7 +6130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:7">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>29000</v>
       </c>
@@ -6151,6 +6154,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G1" xr:uid="{456ABCB0-78C7-4556-BDA1-A91B17080E3B}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
